--- a/test/jupyter notebook/Accel_mode.xlsx
+++ b/test/jupyter notebook/Accel_mode.xlsx
@@ -1,47 +1,50 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BCP_27\Documents\GitHub\Python\test\jupyter notebook\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0242FC4E-3826-48C2-B772-673D4CEBFEBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="615" yWindow="2760" windowWidth="27030" windowHeight="11295" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
-    <t>orders</t>
+    <t xml:space="preserve">orders</t>
   </si>
   <si>
-    <t>sn</t>
+    <t xml:space="preserve">sn</t>
   </si>
   <si>
-    <t>240813685HA4NJ</t>
+    <t xml:space="preserve">240813685HA4NJ</t>
   </si>
   <si>
-    <t>2408136AT6NRM5</t>
+    <t xml:space="preserve">2408136AT6NRM5</t>
   </si>
   <si>
-    <t>2408148RNYAJ6T</t>
+    <t xml:space="preserve">2408148RNYAJ6T</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -50,15 +53,32 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="11"/>
       <name val="Cambria"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -71,33 +91,26 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF8F8FF"/>
+        <bgColor rgb="FFF0F0F0"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="3">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right style="thin">
         <color rgb="FFF0F0F0"/>
@@ -109,73 +122,160 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+  <cellXfs count="5">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFF8F8FF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFF0F0F0"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="1f497d"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="eeece1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4f81bd"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="c0504d"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="9bbb59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="8064a2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4bacc6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="f79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0000ff"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -183,12 +283,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -217,7 +317,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -238,7 +338,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -289,7 +389,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -307,51 +407,56 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="26.28515625" customWidth="1"/>
-    <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
-    <col min="16296" max="16384" width="11.5703125" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="3.51"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
     </row>
   </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/test/jupyter notebook/Accel_mode.xlsx
+++ b/test/jupyter notebook/Accel_mode.xlsx
@@ -1,89 +1,62 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t xml:space="preserve">orders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">240813685HA4NJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2408136AT6NRM5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2408148RNYAJ6T</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="6">
     <font>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <sz val="10"/>
     </font>
     <font>
-      <b val="true"/>
+      <name val="Cambria"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <b val="1"/>
       <sz val="11"/>
-      <name val="Cambria"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="2"/>
       <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -96,21 +69,21 @@
     </fill>
   </fills>
   <borders count="3">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin"/>
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right style="thin">
         <color rgb="FFF0F0F0"/>
@@ -122,60 +95,53 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="Currency" xfId="3" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
+    <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -241,41 +207,41 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -283,180 +249,719 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
+                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:T11"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.55078125" defaultRowHeight="13.5" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="3.51"/>
+    <col width="18.08" customWidth="1" style="5" min="1" max="1"/>
+    <col width="3.51" customWidth="1" style="5" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="0" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>4</v>
+    <row r="1" ht="13.5" customHeight="1" s="6">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>orders</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>sn</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>PR1-000550</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>PR1-000610</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>PR1-000617</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>PR1-000618</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>PR2-000471</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>PR2-000550</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>PR2-000572</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>PR3-000099</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>PR6-000279</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>PR1-000550</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>PR1-000610</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>PR1-000617</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>PR1-000618</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>PR2-000471</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>PR2-000550</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>PR2-000572</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>PR3-000099</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>PR6-000279</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="13.5" customHeight="1" s="6">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>240813685HA4NJ</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>918748B01292AB21AGWH12482</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>X9LT015582</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>XB52020052</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>XB5F012543</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>E72063M3X928299</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>E78352J3N782053</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>CNB1S2S7YT</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>R9KYJ47232</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>E74075C3N705726</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>918748B01292AB21AGWH12482</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>X9LT015582</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>XB52020052</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>XB5F012543</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>E72063M3X928299</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>E78352J3N782053</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>CNB1S2S7YT</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>R9KYJ47232</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>E74075C3N705726</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="13.5" customHeight="1" s="6">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>2408136AT6NRM5</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>918748B01292AB21AGWH12438</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>X9LT015736</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>XB52019962</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>XB5F011485</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>E72063M3X928369</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>E74075A3N640659</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>918748B01292AB21AGWH12438</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>X9LT015736</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>XB52019962</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>XB5F011485</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>E72063M3X928369</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>E74075A3N640659</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="13.5" customHeight="1" s="6">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>2408148RNYAJ6T</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>918748B01292AB21AGWH12494</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>X9LT015770</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>XB52020034</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>E72063M3X927779</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>E74075M2N614368</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>918748B01292AB21AGWH12494</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>X9LT015770</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>XB52020034</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>E72063M3X927779</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>E74075M2N614368</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>X9LT015664</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>XB52019958</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>E72063M3X928277</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>X9LT015664</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>XB52019958</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>E72063M3X928277</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>X9LT016400</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>XB52020047</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>E72063M3X928348</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>X9LT016400</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>XB52020047</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>E72063M3X928348</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>X9LT015706</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>E72063M3X928363</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>X9LT015706</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>E72063M3X928363</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>E72063M3X928296</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>E72063M3X928296</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>E72063M3X928400</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>E72063M3X928400</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>E72063M3X928384</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>E72063M3X928384</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>E72063M3X928335</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>E72063M3X928335</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
--- a/test/jupyter notebook/Accel_mode.xlsx
+++ b/test/jupyter notebook/Accel_mode.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:T11"/>
+  <dimension ref="A1:BC11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.55078125" defaultRowHeight="13.5" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18.08" customWidth="1" style="5" min="1" max="1"/>
@@ -558,49 +558,224 @@
           <t>PR6-000279</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>PR1-000550</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>PR1-000610</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>PR1-000617</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="5" t="inlineStr">
         <is>
           <t>PR1-000618</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="5" t="inlineStr">
         <is>
           <t>PR2-000471</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="5" t="inlineStr">
         <is>
           <t>PR2-000550</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="5" t="inlineStr">
         <is>
           <t>PR2-000572</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="5" t="inlineStr">
         <is>
           <t>PR3-000099</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="5" t="inlineStr">
         <is>
           <t>PR6-000279</t>
+        </is>
+      </c>
+      <c r="U1" s="5" t="inlineStr">
+        <is>
+          <t>PR1-000550</t>
+        </is>
+      </c>
+      <c r="V1" s="5" t="inlineStr">
+        <is>
+          <t>PR1-000610</t>
+        </is>
+      </c>
+      <c r="W1" s="5" t="inlineStr">
+        <is>
+          <t>PR1-000617</t>
+        </is>
+      </c>
+      <c r="X1" s="5" t="inlineStr">
+        <is>
+          <t>PR1-000618</t>
+        </is>
+      </c>
+      <c r="Y1" s="5" t="inlineStr">
+        <is>
+          <t>PR2-000471</t>
+        </is>
+      </c>
+      <c r="Z1" s="5" t="inlineStr">
+        <is>
+          <t>PR2-000550</t>
+        </is>
+      </c>
+      <c r="AA1" s="5" t="inlineStr">
+        <is>
+          <t>PR2-000572</t>
+        </is>
+      </c>
+      <c r="AB1" s="5" t="inlineStr">
+        <is>
+          <t>PR3-000099</t>
+        </is>
+      </c>
+      <c r="AC1" s="5" t="inlineStr">
+        <is>
+          <t>PR6-000279</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>MNL-001561</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>MNL-001633</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>MNL-001743</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>MNL-001850</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>MNL-001856</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>MNL-001886</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>MNL-001887</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>MNL-001941</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>MNL-001942</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>MNL-001943</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>MNL-001944</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>MNL-002018</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>MNL-002034</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>MNL-002040</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>MNL-002049</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>MNL-002052</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>MNL-002057</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>MNL-002066</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>MNL-002088</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>MNL-002095</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>MNL-002110</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>MNL-002120</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>MNL-002124</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>MNL-002126</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>MNL-002139</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>MNL-002144</t>
         </is>
       </c>
     </row>
@@ -655,49 +830,224 @@
           <t>E74075C3N705726</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="5" t="inlineStr">
         <is>
           <t>918748B01292AB21AGWH12482</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="5" t="inlineStr">
         <is>
           <t>X9LT015582</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="5" t="inlineStr">
         <is>
           <t>XB52020052</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" s="5" t="inlineStr">
         <is>
           <t>XB5F012543</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" s="5" t="inlineStr">
         <is>
           <t>E72063M3X928299</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" s="5" t="inlineStr">
         <is>
           <t>E78352J3N782053</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R2" s="5" t="inlineStr">
         <is>
           <t>CNB1S2S7YT</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S2" s="5" t="inlineStr">
         <is>
           <t>R9KYJ47232</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T2" s="5" t="inlineStr">
         <is>
           <t>E74075C3N705726</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="inlineStr">
+        <is>
+          <t>918748B01292AB21AGWH12482</t>
+        </is>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>X9LT015582</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>XB52020052</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>XB5F012543</t>
+        </is>
+      </c>
+      <c r="Y2" s="5" t="inlineStr">
+        <is>
+          <t>E72063M3X928299</t>
+        </is>
+      </c>
+      <c r="Z2" s="5" t="inlineStr">
+        <is>
+          <t>E78352J3N782053</t>
+        </is>
+      </c>
+      <c r="AA2" s="5" t="inlineStr">
+        <is>
+          <t>CNB1S2S7YT</t>
+        </is>
+      </c>
+      <c r="AB2" s="5" t="inlineStr">
+        <is>
+          <t>R9KYJ47232</t>
+        </is>
+      </c>
+      <c r="AC2" s="5" t="inlineStr">
+        <is>
+          <t>E74075C3N705726</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>9XQRB14</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>XFXP7JA002517</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>2QKKL04</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>CMIGA271US1241800002</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>CA9T914603509</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>AFU0100370EZ00468</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>AD40100370KE00081</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>CNC40410N4</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>CNC42015B9</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>CNC3401BR2</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>CNC3190KX4</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>SU4W0RD2V</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>AEH15403Z03792</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>9J70100370FR00667</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>WNK2416E4511</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>W5P241561094</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>9LQ0206128C200418</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>407NTVS4R959</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>AE0EBB3PA100076</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>CE2M114400389</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>AEP11428Z02476</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>XQY242701765</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>X9P240520289</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>CNC4210XKF</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>9ML0100380AC00049</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>AEP20422J01778</t>
         </is>
       </c>
     </row>
@@ -737,34 +1087,139 @@
           <t>E74075A3N640659</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>918748B01292AB21AGWH12438</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>X9LT015736</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>XB52019962</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" s="5" t="inlineStr">
         <is>
           <t>XB5F011485</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" s="5" t="inlineStr">
         <is>
           <t>E72063M3X928369</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T3" s="5" t="inlineStr">
         <is>
           <t>E74075A3N640659</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="inlineStr">
+        <is>
+          <t>918748B01292AB21AGWH12438</t>
+        </is>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>X9LT015736</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>XB52019962</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr">
+        <is>
+          <t>XB5F011485</t>
+        </is>
+      </c>
+      <c r="Y3" s="5" t="inlineStr">
+        <is>
+          <t>E72063M3X928369</t>
+        </is>
+      </c>
+      <c r="AC3" s="5" t="inlineStr">
+        <is>
+          <t>E74075A3N640659</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>XFXP7JA002516</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>2NKKL04</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>CMIGA271US1241800021</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>CA9T914603388</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>AE0EBDAPA100013</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>AD40100370KE00312</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>CNC41535W8</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>CNC3190KYC</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>9J70100370FR00727</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>WNK2347C0175</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>CE2M114400332</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>AEP11428Z02488</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>XQY242701763</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>9ML0100380AC00182</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>AEP20422J01777</t>
         </is>
       </c>
     </row>
@@ -799,29 +1254,89 @@
           <t>E74075M2N614368</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" s="5" t="inlineStr">
         <is>
           <t>918748B01292AB21AGWH12494</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M4" s="5" t="inlineStr">
         <is>
           <t>X9LT015770</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" s="5" t="inlineStr">
         <is>
           <t>XB52020034</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P4" s="5" t="inlineStr">
         <is>
           <t>E72063M3X927779</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T4" s="5" t="inlineStr">
         <is>
           <t>E74075M2N614368</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="inlineStr">
+        <is>
+          <t>918748B01292AB21AGWH12494</t>
+        </is>
+      </c>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>X9LT015770</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr">
+        <is>
+          <t>XB52020034</t>
+        </is>
+      </c>
+      <c r="Y4" s="5" t="inlineStr">
+        <is>
+          <t>E72063M3X927779</t>
+        </is>
+      </c>
+      <c r="AC4" s="5" t="inlineStr">
+        <is>
+          <t>E74075M2N614368</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>HNKKL04</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>CMIGA271US1241800042</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>AE0EBDAPA100020</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>CNC42428GT</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>XQY242701761</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>9ML0100380AC00003</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>AEP20422J01873</t>
         </is>
       </c>
     </row>
@@ -841,19 +1356,54 @@
           <t>E72063M3X928277</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M5" s="5" t="inlineStr">
         <is>
           <t>X9LT015664</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N5" s="5" t="inlineStr">
         <is>
           <t>XB52019958</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P5" s="5" t="inlineStr">
         <is>
           <t>E72063M3X928277</t>
+        </is>
+      </c>
+      <c r="V5" s="5" t="inlineStr">
+        <is>
+          <t>X9LT015664</t>
+        </is>
+      </c>
+      <c r="W5" s="5" t="inlineStr">
+        <is>
+          <t>XB52019958</t>
+        </is>
+      </c>
+      <c r="Y5" s="5" t="inlineStr">
+        <is>
+          <t>E72063M3X928277</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>AE0EBDAPA100017</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>CNC41218RR</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>9ML0100380AC00056</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>AEP20422J01794</t>
         </is>
       </c>
     </row>
@@ -873,19 +1423,54 @@
           <t>E72063M3X928348</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M6" s="5" t="inlineStr">
         <is>
           <t>X9LT016400</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N6" s="5" t="inlineStr">
         <is>
           <t>XB52020047</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P6" s="5" t="inlineStr">
         <is>
           <t>E72063M3X928348</t>
+        </is>
+      </c>
+      <c r="V6" s="5" t="inlineStr">
+        <is>
+          <t>X9LT016400</t>
+        </is>
+      </c>
+      <c r="W6" s="5" t="inlineStr">
+        <is>
+          <t>XB52020047</t>
+        </is>
+      </c>
+      <c r="Y6" s="5" t="inlineStr">
+        <is>
+          <t>E72063M3X928348</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>AE0EBDAPA100004</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>CNC42428HM</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>9ML0100380AC00099</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>AEP20422J01887</t>
         </is>
       </c>
     </row>
@@ -900,14 +1485,29 @@
           <t>E72063M3X928363</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t>X9LT015706</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P7" s="5" t="inlineStr">
         <is>
           <t>E72063M3X928363</t>
+        </is>
+      </c>
+      <c r="V7" s="5" t="inlineStr">
+        <is>
+          <t>X9LT015706</t>
+        </is>
+      </c>
+      <c r="Y7" s="5" t="inlineStr">
+        <is>
+          <t>E72063M3X928363</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>AEP20422J01784</t>
         </is>
       </c>
     </row>
@@ -917,9 +1517,19 @@
           <t>E72063M3X928296</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P8" s="5" t="inlineStr">
         <is>
           <t>E72063M3X928296</t>
+        </is>
+      </c>
+      <c r="Y8" s="5" t="inlineStr">
+        <is>
+          <t>E72063M3X928296</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>AEP20422J01891</t>
         </is>
       </c>
     </row>
@@ -929,9 +1539,19 @@
           <t>E72063M3X928400</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P9" s="5" t="inlineStr">
         <is>
           <t>E72063M3X928400</t>
+        </is>
+      </c>
+      <c r="Y9" s="5" t="inlineStr">
+        <is>
+          <t>E72063M3X928400</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>AEP20422J01770</t>
         </is>
       </c>
     </row>
@@ -941,7 +1561,12 @@
           <t>E72063M3X928384</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P10" s="5" t="inlineStr">
+        <is>
+          <t>E72063M3X928384</t>
+        </is>
+      </c>
+      <c r="Y10" s="5" t="inlineStr">
         <is>
           <t>E72063M3X928384</t>
         </is>
@@ -953,7 +1578,12 @@
           <t>E72063M3X928335</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P11" s="5" t="inlineStr">
+        <is>
+          <t>E72063M3X928335</t>
+        </is>
+      </c>
+      <c r="Y11" s="5" t="inlineStr">
         <is>
           <t>E72063M3X928335</t>
         </is>
